--- a/public/templates/08_설비점검_예비품_만료관리/설비점검_예비품_만료관리.xlsx
+++ b/public/templates/08_설비점검_예비품_만료관리/설비점검_예비품_만료관리.xlsx
@@ -1596,10 +1596,10 @@
         <v>90</v>
       </c>
       <c r="F3" s="12" t="n">
-        <v>46082</v>
+        <v>46091</v>
       </c>
       <c r="G3" s="12" t="n">
-        <v>45056</v>
+        <v>45963</v>
       </c>
       <c r="H3" s="9"/>
     </row>
@@ -1620,10 +1620,10 @@
         <v>180</v>
       </c>
       <c r="F4" s="12" t="n">
-        <v>46063</v>
+        <v>46073</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>44566</v>
+        <v>45945</v>
       </c>
       <c r="H4" s="9"/>
     </row>
@@ -1644,10 +1644,10 @@
         <v>30</v>
       </c>
       <c r="F5" s="12" t="n">
-        <v>46254</v>
+        <v>46156</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>44378</v>
+        <v>45901</v>
       </c>
       <c r="H5" s="9"/>
     </row>
@@ -1668,10 +1668,10 @@
         <v>180</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>46174</v>
+        <v>46117</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>45354</v>
+        <v>46011</v>
       </c>
       <c r="H6" s="9"/>
     </row>
@@ -3710,68 +3710,182 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="12"/>
-      <c r="B3" s="9"/>
+      <c r="A3" s="12" t="n">
+        <v>46193</v>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>EQ001</t>
+        </is>
+      </c>
       <c r="C3" s="15" t="str">
         <f aca="false">IF($B3="","",IFERROR(INDEX(설비목록!$B$3:$B$202,MATCH($B3,설비목록!$A$3:$A$202,0)),"미등록설비"))</f>
-        <v/>
-      </c>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9"/>
+        <v>천장형 에어컨 1호기</v>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>정기점검</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>김담당</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="G3" s="9" t="inlineStr">
+        <is>
+          <t>필터 청소</t>
+        </is>
+      </c>
+      <c r="H3" s="9" t="inlineStr">
+        <is>
+          <t>← 예시 행입니다. 지우고 쓰세요.</t>
+        </is>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="12"/>
-      <c r="B4" s="9"/>
+      <c r="A4" s="12" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>EQ003</t>
+        </is>
+      </c>
       <c r="C4" s="15" t="str">
         <f aca="false">IF($B4="","",IFERROR(INDEX(설비목록!$B$3:$B$202,MATCH($B4,설비목록!$A$3:$A$202,0)),"미등록설비"))</f>
-        <v/>
-      </c>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
+        <v>공기압축기</v>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>정기점검</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>박담당</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>오일 보충 필요</t>
+        </is>
+      </c>
       <c r="H4" s="9"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="12"/>
-      <c r="B5" s="9"/>
+      <c r="A5" s="12" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>EQ003</t>
+        </is>
+      </c>
       <c r="C5" s="15" t="str">
         <f aca="false">IF($B5="","",IFERROR(INDEX(설비목록!$B$3:$B$202,MATCH($B5,설비목록!$A$3:$A$202,0)),"미등록설비"))</f>
-        <v/>
-      </c>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
+        <v>공기압축기</v>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>부품교체</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>박담당</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>압축기 오일 교체</t>
+        </is>
+      </c>
       <c r="H5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="12"/>
-      <c r="B6" s="9"/>
+      <c r="A6" s="12" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>EQ002</t>
+        </is>
+      </c>
       <c r="C6" s="15" t="str">
         <f aca="false">IF($B6="","",IFERROR(INDEX(설비목록!$B$3:$B$202,MATCH($B6,설비목록!$A$3:$A$202,0)),"미등록설비"))</f>
-        <v/>
-      </c>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
+        <v>소화기 (분말 3.3kg)</v>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>정기점검</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>이담당</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>압력 게이지 확인</t>
+        </is>
+      </c>
       <c r="H6" s="9"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="12"/>
-      <c r="B7" s="9"/>
+      <c r="A7" s="12" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>EQ001</t>
+        </is>
+      </c>
       <c r="C7" s="15" t="str">
         <f aca="false">IF($B7="","",IFERROR(INDEX(설비목록!$B$3:$B$202,MATCH($B7,설비목록!$A$3:$A$202,0)),"미등록설비"))</f>
-        <v/>
-      </c>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
+        <v>천장형 에어컨 1호기</v>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>정기점검</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>김담당</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>필터 교체</t>
+        </is>
+      </c>
       <c r="H7" s="9"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14179,14 +14293,14 @@
       </c>
       <c r="B3" s="16" t="n">
         <f aca="true">TODAY()</f>
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>62</v>
       </c>
       <c r="D3" s="17" t="n">
         <f aca="false">SUMPRODUCT(($A$6:$A$205&lt;&gt;"")*($H$6:$H$205&lt;&gt;"")*($H$6:$H$205&lt;=사용안내!$C$17))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E3" s="13" t="s">
         <v>63</v>
@@ -14247,23 +14361,23 @@
       </c>
       <c r="F6" s="20" t="n">
         <f aca="false">IF($A6="","",IF(COUNTIFS(점검이력!$B$3:$B$802,$A6)=0,설비목록!$F3,_xlfn.MAXIFS(점검이력!$A$3:$A$802,점검이력!$B$3:$B$802,$A6)))</f>
-        <v>46082</v>
+        <v>46270</v>
       </c>
       <c r="G6" s="20" t="n">
         <f aca="false">IF(OR($A6="",$F6="",$E6=""),"",$F6+$E6)</f>
-        <v>46172</v>
+        <v>46360</v>
       </c>
       <c r="H6" s="21" t="n">
         <f aca="true">IF($G6="","",$G6-TODAY())</f>
-        <v>-106</v>
+        <v>81</v>
       </c>
       <c r="I6" s="22" t="n">
         <f aca="false">IF($A6="","",COUNTIFS(점검이력!$B$3:$B$802,$A6))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6" s="22" t="str">
         <f aca="false">IF($H6="","",IF($H6&lt;0,"기한초과",IF($H6&lt;=사용안내!$C$17,"임박","정상")))</f>
-        <v>기한초과</v>
+        <v>정상</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14289,23 +14403,23 @@
       </c>
       <c r="F7" s="20" t="n">
         <f aca="false">IF($A7="","",IF(COUNTIFS(점검이력!$B$3:$B$802,$A7)=0,설비목록!$F4,_xlfn.MAXIFS(점검이력!$A$3:$A$802,점검이력!$B$3:$B$802,$A7)))</f>
-        <v>46063</v>
+        <v>46259</v>
       </c>
       <c r="G7" s="20" t="n">
         <f aca="false">IF(OR($A7="",$F7="",$E7=""),"",$F7+$E7)</f>
-        <v>46243</v>
+        <v>46439</v>
       </c>
       <c r="H7" s="21" t="n">
         <f aca="true">IF($G7="","",$G7-TODAY())</f>
-        <v>-35</v>
+        <v>160</v>
       </c>
       <c r="I7" s="22" t="n">
         <f aca="false">IF($A7="","",COUNTIFS(점검이력!$B$3:$B$802,$A7))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" s="22" t="str">
         <f aca="false">IF($H7="","",IF($H7&lt;0,"기한초과",IF($H7&lt;=사용안내!$C$17,"임박","정상")))</f>
-        <v>기한초과</v>
+        <v>정상</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14331,23 +14445,23 @@
       </c>
       <c r="F8" s="20" t="n">
         <f aca="false">IF($A8="","",IF(COUNTIFS(점검이력!$B$3:$B$802,$A8)=0,설비목록!$F5,_xlfn.MAXIFS(점검이력!$A$3:$A$802,점검이력!$B$3:$B$802,$A8)))</f>
-        <v>46254</v>
+        <v>46248</v>
       </c>
       <c r="G8" s="20" t="n">
         <f aca="false">IF(OR($A8="",$F8="",$E8=""),"",$F8+$E8)</f>
-        <v>46284</v>
+        <v>46278</v>
       </c>
       <c r="H8" s="21" t="n">
         <f aca="true">IF($G8="","",$G8-TODAY())</f>
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="I8" s="22" t="n">
         <f aca="false">IF($A8="","",COUNTIFS(점검이력!$B$3:$B$802,$A8))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J8" s="22" t="str">
         <f aca="false">IF($H8="","",IF($H8&lt;0,"기한초과",IF($H8&lt;=사용안내!$C$17,"임박","정상")))</f>
-        <v>임박</v>
+        <v>기한초과</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14373,15 +14487,15 @@
       </c>
       <c r="F9" s="20" t="n">
         <f aca="false">IF($A9="","",IF(COUNTIFS(점검이력!$B$3:$B$802,$A9)=0,설비목록!$F6,_xlfn.MAXIFS(점검이력!$A$3:$A$802,점검이력!$B$3:$B$802,$A9)))</f>
-        <v>46174</v>
+        <v>46117</v>
       </c>
       <c r="G9" s="20" t="n">
         <f aca="false">IF(OR($A9="",$F9="",$E9=""),"",$F9+$E9)</f>
-        <v>46354</v>
+        <v>46297</v>
       </c>
       <c r="H9" s="21" t="n">
         <f aca="true">IF($G9="","",$G9-TODAY())</f>
-        <v>76</v>
+        <v>18</v>
       </c>
       <c r="I9" s="22" t="n">
         <f aca="false">IF($A9="","",COUNTIFS(점검이력!$B$3:$B$802,$A9))</f>
@@ -24628,103 +24742,187 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="12"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9"/>
+      <c r="A3" s="12" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>출고</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>SP002</t>
+        </is>
+      </c>
       <c r="D3" s="15" t="str">
         <f aca="false">IF($C3="","",IFERROR(INDEX(예비품목록!$B$3:$B$202,MATCH($C3,예비품목록!$A$3:$A$202,0)),"미등록품번"))</f>
-        <v/>
+        <v>압축기 오일</v>
       </c>
       <c r="E3" s="15" t="str">
         <f aca="false">IF($C3="","",IFERROR(INDEX(예비품목록!$D$3:$D$202,MATCH($C3,예비품목록!$A$3:$A$202,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="23" t="str">
+        <v>통</v>
+      </c>
+      <c r="F3" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="9" t="inlineStr">
+        <is>
+          <t>EQ003</t>
+        </is>
+      </c>
+      <c r="H3" s="9" t="inlineStr">
+        <is>
+          <t>박담당</t>
+        </is>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>← 예시 행입니다. 지우고 쓰세요.</t>
+        </is>
+      </c>
+      <c r="J3" s="23" t="n">
         <f aca="false">IF(OR($C3="",$F3=""),"",IF($B3="입고",$F3,IF($B3="출고",-$F3,$F3)))</f>
-        <v/>
-      </c>
-      <c r="K3" s="24" t="str">
+        <v>-1</v>
+      </c>
+      <c r="K3" s="24" t="n">
         <f aca="false">IF($C3="","",IFERROR(INDEX(예비품목록!$E$3:$E$202,MATCH($C3,예비품목록!$A$3:$A$202,0)),0)+SUMIFS($J$3:$J3,$C$3:$C3,$C3))</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="12"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
+      <c r="A4" s="12" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>입고</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>SP001</t>
+        </is>
+      </c>
       <c r="D4" s="15" t="str">
         <f aca="false">IF($C4="","",IFERROR(INDEX(예비품목록!$B$3:$B$202,MATCH($C4,예비품목록!$A$3:$A$202,0)),"미등록품번"))</f>
-        <v/>
+        <v>에어컨 필터</v>
       </c>
       <c r="E4" s="15" t="str">
         <f aca="false">IF($C4="","",IFERROR(INDEX(예비품목록!$D$3:$D$202,MATCH($C4,예비품목록!$A$3:$A$202,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F4" s="11"/>
+        <v>EA</v>
+      </c>
+      <c r="F4" s="11" t="n">
+        <v>6</v>
+      </c>
       <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="23" t="str">
+      <c r="H4" s="9" t="inlineStr">
+        <is>
+          <t>김담당</t>
+        </is>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>정기 구매</t>
+        </is>
+      </c>
+      <c r="J4" s="23" t="n">
         <f aca="false">IF(OR($C4="",$F4=""),"",IF($B4="입고",$F4,IF($B4="출고",-$F4,$F4)))</f>
-        <v/>
-      </c>
-      <c r="K4" s="24" t="str">
+        <v>6</v>
+      </c>
+      <c r="K4" s="24" t="n">
         <f aca="false">IF($C4="","",IFERROR(INDEX(예비품목록!$E$3:$E$202,MATCH($C4,예비품목록!$A$3:$A$202,0)),0)+SUMIFS($J$3:$J4,$C$3:$C4,$C4))</f>
-        <v/>
+        <v>14</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="12"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
+      <c r="A5" s="12" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>출고</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>SP001</t>
+        </is>
+      </c>
       <c r="D5" s="15" t="str">
         <f aca="false">IF($C5="","",IFERROR(INDEX(예비품목록!$B$3:$B$202,MATCH($C5,예비품목록!$A$3:$A$202,0)),"미등록품번"))</f>
-        <v/>
+        <v>에어컨 필터</v>
       </c>
       <c r="E5" s="15" t="str">
         <f aca="false">IF($C5="","",IFERROR(INDEX(예비품목록!$D$3:$D$202,MATCH($C5,예비품목록!$A$3:$A$202,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F5" s="11"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
+        <v>EA</v>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>EQ001</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>김담당</t>
+        </is>
+      </c>
       <c r="I5" s="9"/>
-      <c r="J5" s="23" t="str">
+      <c r="J5" s="23" t="n">
         <f aca="false">IF(OR($C5="",$F5=""),"",IF($B5="입고",$F5,IF($B5="출고",-$F5,$F5)))</f>
-        <v/>
-      </c>
-      <c r="K5" s="24" t="str">
+        <v>-2</v>
+      </c>
+      <c r="K5" s="24" t="n">
         <f aca="false">IF($C5="","",IFERROR(INDEX(예비품목록!$E$3:$E$202,MATCH($C5,예비품목록!$A$3:$A$202,0)),0)+SUMIFS($J$3:$J5,$C$3:$C5,$C5))</f>
-        <v/>
+        <v>12</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="12"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
+      <c r="A6" s="12" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>출고</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>SP003</t>
+        </is>
+      </c>
       <c r="D6" s="15" t="str">
         <f aca="false">IF($C6="","",IFERROR(INDEX(예비품목록!$B$3:$B$202,MATCH($C6,예비품목록!$A$3:$A$202,0)),"미등록품번"))</f>
-        <v/>
+        <v>정수기 필터 세트</v>
       </c>
       <c r="E6" s="15" t="str">
         <f aca="false">IF($C6="","",IFERROR(INDEX(예비품목록!$D$3:$D$202,MATCH($C6,예비품목록!$A$3:$A$202,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F6" s="11"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
+        <v>SET</v>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>EQ004</t>
+        </is>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>김담당</t>
+        </is>
+      </c>
       <c r="I6" s="9"/>
-      <c r="J6" s="23" t="str">
+      <c r="J6" s="23" t="n">
         <f aca="false">IF(OR($C6="",$F6=""),"",IF($B6="입고",$F6,IF($B6="출고",-$F6,$F6)))</f>
-        <v/>
-      </c>
-      <c r="K6" s="24" t="str">
+        <v>-1</v>
+      </c>
+      <c r="K6" s="24" t="n">
         <f aca="false">IF($C6="","",IFERROR(INDEX(예비품목록!$E$3:$E$202,MATCH($C6,예비품목록!$A$3:$A$202,0)),0)+SUMIFS($J$3:$J6,$C$3:$C6,$C6))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -39694,7 +39892,7 @@
       </c>
       <c r="B3" s="17" t="n">
         <f aca="false">SUMPRODUCT(($A$6:$A$205&lt;&gt;"")*($G$6:$G$205&gt;0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -39738,15 +39936,15 @@
       </c>
       <c r="D6" s="24" t="n">
         <f aca="false">IF($A6="","",SUMIFS(예비품입출고!$F$3:$F$602,예비품입출고!$C$3:$C$602,$A6,예비품입출고!$B$3:$B$602,"입고"))</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E6" s="24" t="n">
         <f aca="false">IF($A6="","",SUMIFS(예비품입출고!$F$3:$F$602,예비품입출고!$C$3:$C$602,$A6,예비품입출고!$B$3:$B$602,"출고"))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F6" s="24" t="n">
         <f aca="false">IF($A6="","",IF(예비품목록!$E3="",0,예비품목록!$E3)+SUMIFS(예비품입출고!$J$3:$J$602,예비품입출고!$C$3:$C$602,$A6))</f>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G6" s="24" t="n">
         <f aca="false">IF($A6="","",MAX(0,$H6-$F6))</f>
@@ -39776,11 +39974,11 @@
       </c>
       <c r="E7" s="24" t="n">
         <f aca="false">IF($A7="","",SUMIFS(예비품입출고!$F$3:$F$602,예비품입출고!$C$3:$C$602,$A7,예비품입출고!$B$3:$B$602,"출고"))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="24" t="n">
         <f aca="false">IF($A7="","",IF(예비품목록!$E4="",0,예비품목록!$E4)+SUMIFS(예비품입출고!$J$3:$J$602,예비품입출고!$C$3:$C$602,$A7))</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G7" s="24" t="n">
         <f aca="false">IF($A7="","",MAX(0,$H7-$F7))</f>
@@ -39810,15 +40008,15 @@
       </c>
       <c r="E8" s="24" t="n">
         <f aca="false">IF($A8="","",SUMIFS(예비품입출고!$F$3:$F$602,예비품입출고!$C$3:$C$602,$A8,예비품입출고!$B$3:$B$602,"출고"))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="24" t="n">
         <f aca="false">IF($A8="","",IF(예비품목록!$E5="",0,예비품목록!$E5)+SUMIFS(예비품입출고!$J$3:$J$602,예비품입출고!$C$3:$C$602,$A8))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G8" s="24" t="n">
         <f aca="false">IF($A8="","",MAX(0,$H8-$F8))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" s="24" t="n">
         <f aca="false">IF($A8="","",IF(예비품목록!$F5="",0,예비품목록!$F5))</f>
@@ -46632,14 +46830,14 @@
         <v>40</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>46023</v>
+        <v>45931</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>46387</v>
+        <v>46295</v>
       </c>
       <c r="G6" s="26" t="n">
         <f aca="true">IF(OR($F6="",$H6="갱신완료"),"",$F6-TODAY())</f>
-        <v>109</v>
+        <v>16</v>
       </c>
       <c r="H6" s="10" t="s">
         <v>118</v>
@@ -46660,14 +46858,14 @@
         <v>44</v>
       </c>
       <c r="E7" s="12" t="n">
-        <v>45931</v>
+        <v>45996</v>
       </c>
       <c r="F7" s="12" t="n">
-        <v>46295</v>
+        <v>46360</v>
       </c>
       <c r="G7" s="26" t="n">
         <f aca="true">IF(OR($F7="",$H7="갱신완료"),"",$F7-TODAY())</f>
-        <v>17</v>
+        <v>81</v>
       </c>
       <c r="H7" s="10" t="s">
         <v>118</v>
@@ -46688,14 +46886,14 @@
         <v>44</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>46113</v>
+        <v>46082</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>46477</v>
+        <v>46326</v>
       </c>
       <c r="G8" s="26" t="n">
         <f aca="true">IF(OR($F8="",$H8="갱신완료"),"",$F8-TODAY())</f>
-        <v>199</v>
+        <v>47</v>
       </c>
       <c r="H8" s="10" t="s">
         <v>118</v>
